--- a/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00298</v>
+        <v>0.012995</v>
       </c>
       <c r="E2">
-        <v>-0.06725</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.003255671991046905</v>
+        <v>0.09274517684887459</v>
       </c>
       <c r="H2">
-        <v>-0.003255671991046905</v>
+        <v>0.09274517684887459</v>
       </c>
       <c r="I2">
-        <v>0.0507174042452225</v>
+        <v>0.07949291500801441</v>
       </c>
       <c r="J2">
-        <v>0.04992514063277455</v>
+        <v>0.07800021070079607</v>
       </c>
       <c r="K2">
-        <v>272.9</v>
+        <v>53.81</v>
       </c>
       <c r="L2">
-        <v>0.09254925899548953</v>
+        <v>0.01802317792068596</v>
       </c>
       <c r="M2">
-        <v>16.78</v>
+        <v>110.86</v>
       </c>
       <c r="N2">
-        <v>0.004844110854503465</v>
+        <v>0.04414446700911878</v>
       </c>
       <c r="O2">
-        <v>0.06148772444118725</v>
+        <v>2.060211856532243</v>
       </c>
       <c r="P2">
-        <v>16.78</v>
+        <v>110.86</v>
       </c>
       <c r="Q2">
-        <v>0.004844110854503465</v>
+        <v>0.04414446700911878</v>
       </c>
       <c r="R2">
-        <v>0.06148772444118725</v>
+        <v>2.060211856532243</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2629.6</v>
+        <v>2307.2</v>
       </c>
       <c r="V2">
-        <v>0.7591224018475751</v>
+        <v>0.9187273523672999</v>
       </c>
       <c r="W2">
-        <v>0.06913537707590908</v>
+        <v>0.04804047450571645</v>
       </c>
       <c r="X2">
-        <v>0.0630460889562094</v>
+        <v>0.104854930638571</v>
       </c>
       <c r="Y2">
-        <v>0.006089288119699679</v>
+        <v>-0.05681445613285454</v>
       </c>
       <c r="Z2">
-        <v>0.7217965912072137</v>
+        <v>0.7562588235642019</v>
       </c>
       <c r="AA2">
-        <v>0.06961354374731554</v>
+        <v>0.1002308434718495</v>
       </c>
       <c r="AB2">
-        <v>0.05529277003932398</v>
+        <v>0.09060145478673037</v>
       </c>
       <c r="AC2">
-        <v>0.01432077370799157</v>
+        <v>0.009629388685119124</v>
       </c>
       <c r="AD2">
-        <v>1653.3</v>
+        <v>1791.1</v>
       </c>
       <c r="AE2">
-        <v>0.42295051056207</v>
+        <v>0.1547647603609457</v>
       </c>
       <c r="AF2">
-        <v>1653.722950510562</v>
+        <v>1791.254764760361</v>
       </c>
       <c r="AG2">
-        <v>-975.8770494894379</v>
+        <v>-515.9452352396393</v>
       </c>
       <c r="AH2">
-        <v>0.3231364742684206</v>
+        <v>0.4163235246722369</v>
       </c>
       <c r="AI2">
-        <v>0.2503849083302919</v>
+        <v>0.2878509675180153</v>
       </c>
       <c r="AJ2">
-        <v>-0.392214158584562</v>
+        <v>-0.2585731842535798</v>
       </c>
       <c r="AK2">
-        <v>-0.245496066823316</v>
+        <v>-0.1317647408252079</v>
       </c>
       <c r="AL2">
-        <v>26.888</v>
+        <v>34.24</v>
       </c>
       <c r="AM2">
-        <v>26.888</v>
+        <v>34.24</v>
       </c>
       <c r="AN2">
-        <v>9.478029065267865</v>
+        <v>6.897733618315907</v>
       </c>
       <c r="AO2">
-        <v>5.548943766736091</v>
+        <v>6.927570093457943</v>
       </c>
       <c r="AP2">
-        <v>-5.594502533834597</v>
+        <v>-1.986964878746228</v>
       </c>
       <c r="AQ2">
-        <v>5.548943766736091</v>
+        <v>6.927570093457943</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00784</v>
+        <v>0.0333</v>
       </c>
       <c r="E3">
-        <v>0.102</v>
+        <v>0.306</v>
       </c>
       <c r="G3">
-        <v>0.2088974854932302</v>
+        <v>0.2300724637681159</v>
       </c>
       <c r="H3">
-        <v>0.2088974854932302</v>
+        <v>0.2300724637681159</v>
       </c>
       <c r="I3">
-        <v>0.2572533849129594</v>
+        <v>0.2155797101449275</v>
       </c>
       <c r="J3">
-        <v>0.2571953578336557</v>
+        <v>0.2154883628101203</v>
       </c>
       <c r="K3">
-        <v>13.3</v>
+        <v>11.8</v>
       </c>
       <c r="L3">
-        <v>0.2572533849129594</v>
+        <v>0.213768115942029</v>
       </c>
       <c r="M3">
-        <v>3.28</v>
+        <v>4.86</v>
       </c>
       <c r="N3">
-        <v>0.01299524564183835</v>
+        <v>0.03011152416356877</v>
       </c>
       <c r="O3">
-        <v>0.2466165413533834</v>
+        <v>0.411864406779661</v>
       </c>
       <c r="P3">
-        <v>3.28</v>
+        <v>4.86</v>
       </c>
       <c r="Q3">
-        <v>0.01299524564183835</v>
+        <v>0.03011152416356877</v>
       </c>
       <c r="R3">
-        <v>0.2466165413533834</v>
+        <v>0.411864406779661</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>38.8</v>
+        <v>21.8</v>
       </c>
       <c r="V3">
-        <v>0.1537242472266244</v>
+        <v>0.1350681536555143</v>
       </c>
       <c r="W3">
-        <v>0.08866666666666667</v>
+        <v>0.0845272206303725</v>
       </c>
       <c r="X3">
-        <v>0.05273219062241002</v>
+        <v>0.08726025360230658</v>
       </c>
       <c r="Y3">
-        <v>0.03593447604425665</v>
+        <v>-0.002733032971934071</v>
       </c>
       <c r="Z3">
-        <v>0.5379812695109262</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="AA3">
-        <v>0.138366285119667</v>
+        <v>0.1180055320150659</v>
       </c>
       <c r="AB3">
-        <v>0.05273219062241002</v>
+        <v>0.08703029421690751</v>
       </c>
       <c r="AC3">
-        <v>0.08563409449725701</v>
+        <v>0.0309752377981584</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG3">
-        <v>-38.8</v>
+        <v>-20.6</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.007380073800738007</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.007863695937090432</v>
       </c>
       <c r="AJ3">
-        <v>-0.1816479400749063</v>
+        <v>-0.1463068181818182</v>
       </c>
       <c r="AK3">
-        <v>-0.3849206349206349</v>
+        <v>-0.1574923547400612</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.08955223880597014</v>
       </c>
       <c r="AP3">
-        <v>-2.604026845637584</v>
+        <v>-1.537313432835821</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Doha Insurance Group Q.P.S.C. (DSM:DOHI)</t>
+          <t>Qatar Insurance Company Q.S.P.C. (DSM:QATI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +850,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.209</v>
-      </c>
-      <c r="E4">
-        <v>-0.06660000000000001</v>
+        <v>-0.00747</v>
       </c>
       <c r="G4">
-        <v>0.1681159420289855</v>
+        <v>0.0795509822263798</v>
       </c>
       <c r="H4">
-        <v>0.1681159420289855</v>
+        <v>0.0795509822263798</v>
       </c>
       <c r="I4">
-        <v>0.1710144927536232</v>
+        <v>0.06716557530402245</v>
       </c>
       <c r="J4">
-        <v>0.1709521437198068</v>
+        <v>0.0638576078311839</v>
       </c>
       <c r="K4">
-        <v>19.2</v>
+        <v>-3.59</v>
       </c>
       <c r="L4">
-        <v>0.1391304347826087</v>
+        <v>-0.001343311506080449</v>
       </c>
       <c r="M4">
-        <v>13.5</v>
+        <v>89.7</v>
       </c>
       <c r="N4">
-        <v>0.05119453924914676</v>
+        <v>0.05199397171342453</v>
       </c>
       <c r="O4">
-        <v>0.703125</v>
+        <v>-24.98607242339833</v>
       </c>
       <c r="P4">
-        <v>13.5</v>
+        <v>89.7</v>
       </c>
       <c r="Q4">
-        <v>0.05119453924914676</v>
+        <v>0.05199397171342453</v>
       </c>
       <c r="R4">
-        <v>0.703125</v>
+        <v>-24.98607242339833</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>36.7</v>
+        <v>2145.9</v>
       </c>
       <c r="V4">
-        <v>0.1391733029958286</v>
+        <v>1.243855784836541</v>
       </c>
       <c r="W4">
-        <v>0.06557377049180327</v>
+        <v>-0.001175199685740474</v>
       </c>
       <c r="X4">
-        <v>0.05992469121918462</v>
+        <v>0.1150090481063251</v>
       </c>
       <c r="Y4">
-        <v>0.005649079272618644</v>
+        <v>-0.1161842477920656</v>
       </c>
       <c r="Z4">
-        <v>0.5259146341463415</v>
+        <v>1.75464513163942</v>
       </c>
       <c r="AA4">
-        <v>0.08990623412093497</v>
+        <v>0.1120474406991261</v>
       </c>
       <c r="AB4">
-        <v>0.0551275758438439</v>
+        <v>0.09184770870007614</v>
       </c>
       <c r="AC4">
-        <v>0.03477865827709108</v>
+        <v>0.02019973199904997</v>
       </c>
       <c r="AD4">
-        <v>56</v>
+        <v>1117.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>56</v>
+        <v>1117.8</v>
       </c>
       <c r="AG4">
+        <v>-1028.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.3931762223003869</v>
+      </c>
+      <c r="AI4">
+        <v>0.306011826544021</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.474824271983934</v>
+      </c>
+      <c r="AK4">
+        <v>-0.6822615966553853</v>
+      </c>
+      <c r="AL4">
         <v>19.3</v>
       </c>
-      <c r="AH4">
-        <v>0.1751642164529246</v>
-      </c>
-      <c r="AI4">
-        <v>0.1494130202774813</v>
-      </c>
-      <c r="AJ4">
-        <v>0.06819787985865723</v>
-      </c>
-      <c r="AK4">
-        <v>0.05708370304643595</v>
-      </c>
-      <c r="AL4">
-        <v>0.588</v>
-      </c>
       <c r="AM4">
-        <v>0.588</v>
+        <v>19.3</v>
       </c>
       <c r="AN4">
-        <v>2.121212121212121</v>
+        <v>5.726434426229508</v>
       </c>
       <c r="AO4">
-        <v>40.13605442176871</v>
+        <v>9.300518134715025</v>
       </c>
       <c r="AP4">
-        <v>0.731060606060606</v>
+        <v>-5.266905737704919</v>
       </c>
       <c r="AQ4">
-        <v>40.13605442176871</v>
+        <v>9.300518134715025</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qatar Insurance Company Q.S.P.C. (DSM:QATI)</t>
+          <t>Doha Insurance Group Q.P.S.C. (DSM:DOHI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,118 +981,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0138</v>
+        <v>0.129</v>
       </c>
       <c r="E5">
-        <v>-0.0679</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G5">
-        <v>-0.0308121167069318</v>
+        <v>0.1536441234405778</v>
       </c>
       <c r="H5">
-        <v>-0.0308121167069318</v>
+        <v>0.1536441234405778</v>
       </c>
       <c r="I5">
-        <v>0.03434305891098309</v>
+        <v>0.1963230466185161</v>
       </c>
       <c r="J5">
-        <v>0.03321847924120971</v>
+        <v>0.1962761435015765</v>
       </c>
       <c r="K5">
-        <v>205.1</v>
+        <v>29.3</v>
       </c>
       <c r="L5">
-        <v>0.07623118379483367</v>
+        <v>0.1923834537097833</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>16.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05997056659308315</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.5563139931740615</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>16.3</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05997056659308315</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.5563139931740615</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>2510.4</v>
+        <v>63.5</v>
       </c>
       <c r="V5">
-        <v>1.017509727626459</v>
+        <v>0.2336276674025018</v>
       </c>
       <c r="W5">
-        <v>0.07269698366001488</v>
+        <v>0.09190715181932246</v>
       </c>
       <c r="X5">
-        <v>0.06616748669323419</v>
+        <v>0.09470081317081688</v>
       </c>
       <c r="Y5">
-        <v>0.006529496966780693</v>
+        <v>-0.00279366135149442</v>
       </c>
       <c r="Z5">
-        <v>1.484741460184316</v>
+        <v>0.4504584442472641</v>
       </c>
       <c r="AA5">
-        <v>0.04932085337369611</v>
+        <v>0.08841424624457291</v>
       </c>
       <c r="AB5">
-        <v>0.05545796423480406</v>
+        <v>0.08935520087338462</v>
       </c>
       <c r="AC5">
-        <v>-0.006137110861107943</v>
+        <v>-0.0009409546288117188</v>
       </c>
       <c r="AD5">
-        <v>978.7</v>
+        <v>48.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>978.7</v>
+        <v>48.7</v>
       </c>
       <c r="AG5">
-        <v>-1531.7</v>
+        <v>-14.8</v>
       </c>
       <c r="AH5">
-        <v>0.2840186888766361</v>
+        <v>0.1519500780031201</v>
       </c>
       <c r="AI5">
-        <v>0.2410472390522635</v>
+        <v>0.1291092258748675</v>
       </c>
       <c r="AJ5">
-        <v>-1.63730625334046</v>
+        <v>-0.05758754863813229</v>
       </c>
       <c r="AK5">
-        <v>-0.9883210736869275</v>
+        <v>-0.04717883328020401</v>
       </c>
       <c r="AL5">
-        <v>11</v>
+        <v>0.64</v>
       </c>
       <c r="AM5">
-        <v>11</v>
+        <v>0.64</v>
       </c>
       <c r="AN5">
-        <v>8.785457809694794</v>
+        <v>1.484756097560976</v>
       </c>
       <c r="AO5">
-        <v>8.4</v>
+        <v>46.71875</v>
       </c>
       <c r="AP5">
-        <v>-13.74955116696589</v>
+        <v>-0.4512195121951219</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>46.71875</v>
       </c>
     </row>
     <row r="6">
@@ -1115,28 +1115,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.147</v>
+        <v>-0.00731</v>
       </c>
       <c r="E6">
-        <v>-0.333</v>
+        <v>-0.0177</v>
       </c>
       <c r="G6">
-        <v>0.5737226277372263</v>
+        <v>0.2670454545454545</v>
       </c>
       <c r="H6">
-        <v>0.5737226277372263</v>
+        <v>0.2670454545454545</v>
       </c>
       <c r="I6">
-        <v>0.295626421866972</v>
+        <v>0.1518375667417407</v>
       </c>
       <c r="J6">
-        <v>0.2870092261657433</v>
+        <v>0.1480116031955929</v>
       </c>
       <c r="K6">
-        <v>35.3</v>
+        <v>16.3</v>
       </c>
       <c r="L6">
-        <v>0.5153284671532846</v>
+        <v>0.1543560606060606</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1160,73 +1160,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>43.7</v>
+        <v>76</v>
       </c>
       <c r="V6">
-        <v>0.09090909090909091</v>
+        <v>0.2153584584868235</v>
       </c>
       <c r="W6">
-        <v>0.02587976539589443</v>
+        <v>0.01155372838106039</v>
       </c>
       <c r="X6">
-        <v>0.09634706623284092</v>
+        <v>0.1634898248780788</v>
       </c>
       <c r="Y6">
-        <v>-0.07046730083694649</v>
+        <v>-0.1519360964970184</v>
       </c>
       <c r="Z6">
-        <v>0.03577727927147926</v>
+        <v>0.05317609418065528</v>
       </c>
       <c r="AA6">
-        <v>0.01026840923802295</v>
+        <v>0.007870678951358625</v>
       </c>
       <c r="AB6">
-        <v>0.05654689120517689</v>
+        <v>0.09709616274735136</v>
       </c>
       <c r="AC6">
-        <v>-0.04627848196715394</v>
+        <v>-0.08922548379599274</v>
       </c>
       <c r="AD6">
-        <v>618.6</v>
+        <v>623.4</v>
       </c>
       <c r="AE6">
-        <v>0.42295051056207</v>
+        <v>0.1547647603609457</v>
       </c>
       <c r="AF6">
-        <v>619.0229505105621</v>
+        <v>623.554764760361</v>
       </c>
       <c r="AG6">
-        <v>575.322950510562</v>
+        <v>547.554764760361</v>
       </c>
       <c r="AH6">
-        <v>0.5628899080656377</v>
+        <v>0.6385905289871694</v>
       </c>
       <c r="AI6">
-        <v>0.3049189460938225</v>
+        <v>0.30562593237399</v>
       </c>
       <c r="AJ6">
-        <v>0.5448015596937614</v>
+        <v>0.6080869202864203</v>
       </c>
       <c r="AK6">
-        <v>0.2896276195171271</v>
+        <v>0.2787595451383124</v>
       </c>
       <c r="AL6">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="AM6">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="AN6">
-        <v>28.46100759144237</v>
+        <v>34.13085135505064</v>
       </c>
       <c r="AO6">
-        <v>1.300653594771242</v>
+        <v>1.111888111888112</v>
       </c>
       <c r="AP6">
-        <v>26.46988500163616</v>
+        <v>29.97836105997049</v>
       </c>
       <c r="AQ6">
-        <v>1.300653594771242</v>
+        <v>1.111888111888112</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.012995</v>
+        <v>0.043215</v>
       </c>
       <c r="E2">
-        <v>0.06759999999999999</v>
+        <v>0.3975</v>
       </c>
       <c r="G2">
-        <v>0.09274517684887459</v>
+        <v>0.06459671663097787</v>
       </c>
       <c r="H2">
-        <v>0.09274517684887459</v>
+        <v>0.06459671663097787</v>
       </c>
       <c r="I2">
-        <v>0.07949291500801441</v>
+        <v>0.1085798186891249</v>
       </c>
       <c r="J2">
-        <v>0.07800021070079607</v>
+        <v>0.1069814136978609</v>
       </c>
       <c r="K2">
-        <v>53.81</v>
+        <v>-115.4</v>
       </c>
       <c r="L2">
-        <v>0.01802317792068596</v>
+        <v>-0.04576096439051471</v>
       </c>
       <c r="M2">
-        <v>110.86</v>
+        <v>28.074</v>
       </c>
       <c r="N2">
-        <v>0.04414446700911878</v>
+        <v>0.008736268865722733</v>
       </c>
       <c r="O2">
-        <v>2.060211856532243</v>
+        <v>-0.2432755632582323</v>
       </c>
       <c r="P2">
-        <v>110.86</v>
+        <v>28.074</v>
       </c>
       <c r="Q2">
-        <v>0.04414446700911878</v>
+        <v>0.008736268865722733</v>
       </c>
       <c r="R2">
-        <v>2.060211856532243</v>
+        <v>-0.2432755632582323</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2307.2</v>
+        <v>564.3</v>
       </c>
       <c r="V2">
-        <v>0.9187273523672999</v>
+        <v>0.1756029251594834</v>
       </c>
       <c r="W2">
-        <v>0.04804047450571645</v>
+        <v>0.04928729238034837</v>
       </c>
       <c r="X2">
-        <v>0.104854930638571</v>
+        <v>0.08017613765714045</v>
       </c>
       <c r="Y2">
-        <v>-0.05681445613285454</v>
+        <v>-0.03088884527679207</v>
       </c>
       <c r="Z2">
-        <v>0.7562588235642019</v>
+        <v>0.6491316742852689</v>
       </c>
       <c r="AA2">
-        <v>0.1002308434718495</v>
+        <v>0.1257511613995498</v>
       </c>
       <c r="AB2">
-        <v>0.09060145478673037</v>
+        <v>0.07626000355310386</v>
       </c>
       <c r="AC2">
-        <v>0.009629388685119124</v>
+        <v>0.04982686197366357</v>
       </c>
       <c r="AD2">
-        <v>1791.1</v>
+        <v>1216.13</v>
       </c>
       <c r="AE2">
-        <v>0.1547647603609457</v>
+        <v>0.1820661488242576</v>
       </c>
       <c r="AF2">
-        <v>1791.254764760361</v>
+        <v>1216.312066148824</v>
       </c>
       <c r="AG2">
-        <v>-515.9452352396393</v>
+        <v>652.0120661488243</v>
       </c>
       <c r="AH2">
-        <v>0.4163235246722369</v>
+        <v>0.2745741914072345</v>
       </c>
       <c r="AI2">
-        <v>0.2878509675180153</v>
+        <v>0.2340676702820182</v>
       </c>
       <c r="AJ2">
-        <v>-0.2585731842535798</v>
+        <v>0.1686741769243572</v>
       </c>
       <c r="AK2">
-        <v>-0.1317647408252079</v>
+        <v>0.1407591303573345</v>
       </c>
       <c r="AL2">
-        <v>34.24</v>
+        <v>63.802</v>
       </c>
       <c r="AM2">
-        <v>34.24</v>
+        <v>63.802</v>
       </c>
       <c r="AN2">
-        <v>6.897733618315907</v>
+        <v>4.201331430960089</v>
       </c>
       <c r="AO2">
-        <v>6.927570093457943</v>
+        <v>4.289207234882919</v>
       </c>
       <c r="AP2">
-        <v>-1.986964878746228</v>
+        <v>2.252488456724432</v>
       </c>
       <c r="AQ2">
-        <v>6.927570093457943</v>
+        <v>4.289207234882919</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Khaleej Takaful Insurance Company Q.P.S.C. (DSM:AKHI)</t>
+          <t>Doha Insurance Group Q.P.S.C. (DSM:DOHI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0333</v>
+        <v>0.167</v>
       </c>
       <c r="E3">
-        <v>0.306</v>
+        <v>0.277</v>
       </c>
       <c r="G3">
-        <v>0.2300724637681159</v>
+        <v>0.1758474576271186</v>
       </c>
       <c r="H3">
-        <v>0.2300724637681159</v>
+        <v>0.1758474576271186</v>
       </c>
       <c r="I3">
-        <v>0.2155797101449275</v>
+        <v>0.2208686440677966</v>
       </c>
       <c r="J3">
-        <v>0.2154883628101203</v>
+        <v>0.2208244703389831</v>
       </c>
       <c r="K3">
-        <v>11.8</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>0.213768115942029</v>
+        <v>0.211864406779661</v>
       </c>
       <c r="M3">
-        <v>4.86</v>
+        <v>20.6</v>
       </c>
       <c r="N3">
-        <v>0.03011152416356877</v>
+        <v>0.06274748705452331</v>
       </c>
       <c r="O3">
-        <v>0.411864406779661</v>
+        <v>0.515</v>
       </c>
       <c r="P3">
-        <v>4.86</v>
+        <v>20.6</v>
       </c>
       <c r="Q3">
-        <v>0.03011152416356877</v>
+        <v>0.06274748705452331</v>
       </c>
       <c r="R3">
-        <v>0.411864406779661</v>
+        <v>0.515</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>21.8</v>
+        <v>51.4</v>
       </c>
       <c r="V3">
-        <v>0.1350681536555143</v>
+        <v>0.1565641181845873</v>
       </c>
       <c r="W3">
-        <v>0.0845272206303725</v>
+        <v>0.121765601217656</v>
       </c>
       <c r="X3">
-        <v>0.08726025360230658</v>
+        <v>0.07711541243361558</v>
       </c>
       <c r="Y3">
-        <v>-0.002733032971934071</v>
+        <v>0.04465018878404042</v>
       </c>
       <c r="Z3">
-        <v>0.5476190476190477</v>
+        <v>0.6018489002231432</v>
       </c>
       <c r="AA3">
-        <v>0.1180055320150659</v>
+        <v>0.1329029646158751</v>
       </c>
       <c r="AB3">
-        <v>0.08703029421690751</v>
+        <v>0.07568528559347776</v>
       </c>
       <c r="AC3">
-        <v>0.0309752377981584</v>
+        <v>0.0572176790223973</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>21.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.2</v>
+        <v>21.7</v>
       </c>
       <c r="AG3">
-        <v>-20.6</v>
+        <v>-29.7</v>
       </c>
       <c r="AH3">
-        <v>0.007380073800738007</v>
+        <v>0.062</v>
       </c>
       <c r="AI3">
-        <v>0.007863695937090432</v>
+        <v>0.06300813008130081</v>
       </c>
       <c r="AJ3">
-        <v>-0.1463068181818182</v>
+        <v>-0.09946416610850635</v>
       </c>
       <c r="AK3">
-        <v>-0.1574923547400612</v>
+        <v>-0.1013651877133106</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="AN3">
-        <v>0.08955223880597014</v>
+        <v>0.4854586129753914</v>
+      </c>
+      <c r="AO3">
+        <v>138.0794701986755</v>
       </c>
       <c r="AP3">
-        <v>-1.537313432835821</v>
+        <v>-0.6644295302013422</v>
+      </c>
+      <c r="AQ3">
+        <v>138.0794701986755</v>
       </c>
     </row>
     <row r="4">
@@ -850,43 +856,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00747</v>
+        <v>-0.0757</v>
       </c>
       <c r="G4">
-        <v>0.0795509822263798</v>
+        <v>0.04780326056921801</v>
       </c>
       <c r="H4">
-        <v>0.0795509822263798</v>
+        <v>0.04780326056921801</v>
       </c>
       <c r="I4">
-        <v>0.06716557530402245</v>
+        <v>0.09565257437597863</v>
       </c>
       <c r="J4">
-        <v>0.0638576078311839</v>
+        <v>0.09003929348491646</v>
       </c>
       <c r="K4">
-        <v>-3.59</v>
+        <v>-14.5</v>
       </c>
       <c r="L4">
-        <v>-0.001343311506080449</v>
+        <v>-0.00667771944367689</v>
       </c>
       <c r="M4">
-        <v>89.7</v>
+        <v>0.75</v>
       </c>
       <c r="N4">
-        <v>0.05199397171342453</v>
+        <v>0.0003227750043036667</v>
       </c>
       <c r="O4">
-        <v>-24.98607242339833</v>
+        <v>-0.05172413793103448</v>
       </c>
       <c r="P4">
-        <v>89.7</v>
+        <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>0.05199397171342453</v>
+        <v>0.0003227750043036667</v>
       </c>
       <c r="R4">
-        <v>-24.98607242339833</v>
+        <v>-0.05172413793103448</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,73 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2145.9</v>
+        <v>404.9</v>
       </c>
       <c r="V4">
-        <v>1.243855784836541</v>
+        <v>0.1742554656567395</v>
       </c>
       <c r="W4">
-        <v>-0.001175199685740474</v>
+        <v>-0.00578472831724248</v>
       </c>
       <c r="X4">
-        <v>0.1150090481063251</v>
+        <v>0.08323686288066531</v>
       </c>
       <c r="Y4">
-        <v>-0.1161842477920656</v>
+        <v>-0.0890215911979078</v>
       </c>
       <c r="Z4">
-        <v>1.75464513163942</v>
+        <v>1.468650659452148</v>
       </c>
       <c r="AA4">
-        <v>0.1120474406991261</v>
+        <v>0.132236267753228</v>
       </c>
       <c r="AB4">
-        <v>0.09184770870007614</v>
+        <v>0.07683472151272996</v>
       </c>
       <c r="AC4">
-        <v>0.02019973199904997</v>
+        <v>0.05540154624049806</v>
       </c>
       <c r="AD4">
-        <v>1117.8</v>
+        <v>590.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1117.8</v>
+        <v>590.6</v>
       </c>
       <c r="AG4">
-        <v>-1028.1</v>
+        <v>185.7</v>
       </c>
       <c r="AH4">
-        <v>0.3931762223003869</v>
+        <v>0.202662823416375</v>
       </c>
       <c r="AI4">
-        <v>0.306011826544021</v>
+        <v>0.2072062589902817</v>
       </c>
       <c r="AJ4">
-        <v>-1.474824271983934</v>
+        <v>0.07400470250667518</v>
       </c>
       <c r="AK4">
-        <v>-0.6822615966553853</v>
+        <v>0.0759384967694447</v>
       </c>
       <c r="AL4">
-        <v>19.3</v>
+        <v>39</v>
       </c>
       <c r="AM4">
-        <v>19.3</v>
+        <v>39</v>
       </c>
       <c r="AN4">
-        <v>5.726434426229508</v>
+        <v>2.711662075298439</v>
       </c>
       <c r="AO4">
-        <v>9.300518134715025</v>
+        <v>5.325641025641025</v>
       </c>
       <c r="AP4">
-        <v>-5.266905737704919</v>
+        <v>0.8526170798898073</v>
       </c>
       <c r="AQ4">
-        <v>9.300518134715025</v>
+        <v>5.325641025641025</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Doha Insurance Group Q.P.S.C. (DSM:DOHI)</t>
+          <t>Al Khaleej Takaful Insurance Company Q.P.S.C. (DSM:AKHI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,46 +987,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.129</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="E5">
-        <v>0.06759999999999999</v>
+        <v>0.518</v>
       </c>
       <c r="G5">
-        <v>0.1536441234405778</v>
+        <v>0.242566510172144</v>
       </c>
       <c r="H5">
-        <v>0.1536441234405778</v>
+        <v>0.242566510172144</v>
       </c>
       <c r="I5">
-        <v>0.1963230466185161</v>
+        <v>0.244131455399061</v>
       </c>
       <c r="J5">
-        <v>0.1962761435015765</v>
+        <v>0.244131455399061</v>
       </c>
       <c r="K5">
-        <v>29.3</v>
+        <v>15.8</v>
       </c>
       <c r="L5">
-        <v>0.1923834537097833</v>
+        <v>0.2472613458528952</v>
       </c>
       <c r="M5">
-        <v>16.3</v>
+        <v>6.57</v>
       </c>
       <c r="N5">
-        <v>0.05997056659308315</v>
+        <v>0.03154104656745079</v>
       </c>
       <c r="O5">
-        <v>0.5563139931740615</v>
+        <v>0.4158227848101266</v>
       </c>
       <c r="P5">
-        <v>16.3</v>
+        <v>6.57</v>
       </c>
       <c r="Q5">
-        <v>0.05997056659308315</v>
+        <v>0.03154104656745079</v>
       </c>
       <c r="R5">
-        <v>0.5563139931740615</v>
+        <v>0.4158227848101266</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,73 +1035,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>63.5</v>
+        <v>28.7</v>
       </c>
       <c r="V5">
-        <v>0.2336276674025018</v>
+        <v>0.1377820451272203</v>
       </c>
       <c r="W5">
-        <v>0.09190715181932246</v>
+        <v>0.1043593130779392</v>
       </c>
       <c r="X5">
-        <v>0.09470081317081688</v>
+        <v>0.07514064091721216</v>
       </c>
       <c r="Y5">
-        <v>-0.00279366135149442</v>
+        <v>0.02921867216072707</v>
       </c>
       <c r="Z5">
-        <v>0.4504584442472641</v>
+        <v>0.4885321100917432</v>
       </c>
       <c r="AA5">
-        <v>0.08841424624457291</v>
+        <v>0.1192660550458716</v>
       </c>
       <c r="AB5">
-        <v>0.08935520087338462</v>
+        <v>0.0750138773390425</v>
       </c>
       <c r="AC5">
-        <v>-0.0009409546288117188</v>
+        <v>0.04425217770682907</v>
       </c>
       <c r="AD5">
-        <v>48.7</v>
+        <v>1.13</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>48.7</v>
+        <v>1.13</v>
       </c>
       <c r="AG5">
-        <v>-14.8</v>
+        <v>-27.57</v>
       </c>
       <c r="AH5">
-        <v>0.1519500780031201</v>
+        <v>0.005395597574368523</v>
       </c>
       <c r="AI5">
-        <v>0.1291092258748675</v>
+        <v>0.007078869886612792</v>
       </c>
       <c r="AJ5">
-        <v>-0.05758754863813229</v>
+        <v>-0.1525479997786754</v>
       </c>
       <c r="AK5">
-        <v>-0.04717883328020401</v>
+        <v>-0.2105705338730619</v>
       </c>
       <c r="AL5">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.484756097560976</v>
-      </c>
-      <c r="AO5">
-        <v>46.71875</v>
+        <v>0.06608187134502923</v>
       </c>
       <c r="AP5">
-        <v>-0.4512195121951219</v>
-      </c>
-      <c r="AQ5">
-        <v>46.71875</v>
+        <v>-1.612280701754386</v>
       </c>
     </row>
     <row r="6">
@@ -1115,118 +1115,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00731</v>
-      </c>
-      <c r="E6">
-        <v>-0.0177</v>
+        <v>0.007229999999999999</v>
       </c>
       <c r="G6">
-        <v>0.2670454545454545</v>
+        <v>0.1064483111566018</v>
       </c>
       <c r="H6">
-        <v>0.2670454545454545</v>
+        <v>0.1064483111566018</v>
       </c>
       <c r="I6">
-        <v>0.1518375667417407</v>
+        <v>0.09024142037088176</v>
       </c>
       <c r="J6">
-        <v>0.1480116031955929</v>
+        <v>0.09024142037088176</v>
       </c>
       <c r="K6">
-        <v>16.3</v>
+        <v>-156.7</v>
       </c>
       <c r="L6">
-        <v>0.1543560606060606</v>
+        <v>-1.60388945752303</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.154</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.0004358901783187093</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>-0.0009827696234843651</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.154</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.0004358901783187093</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>-0.0009827696234843651</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>76</v>
+        <v>79.3</v>
       </c>
       <c r="V6">
-        <v>0.2153584584868235</v>
+        <v>0.2244551372771016</v>
       </c>
       <c r="W6">
-        <v>0.01155372838106039</v>
+        <v>-0.1107968606377713</v>
       </c>
       <c r="X6">
-        <v>0.1634898248780788</v>
+        <v>0.1305044210073297</v>
       </c>
       <c r="Y6">
-        <v>-0.1519360964970184</v>
+        <v>-0.2413012816451011</v>
       </c>
       <c r="Z6">
-        <v>0.05317609418065528</v>
+        <v>0.04979911977674844</v>
       </c>
       <c r="AA6">
-        <v>0.007870678951358625</v>
+        <v>0.004493943301873447</v>
       </c>
       <c r="AB6">
-        <v>0.09709616274735136</v>
+        <v>0.08229844230270678</v>
       </c>
       <c r="AC6">
-        <v>-0.08922548379599274</v>
+        <v>-0.07780449900083333</v>
       </c>
       <c r="AD6">
-        <v>623.4</v>
+        <v>602.7</v>
       </c>
       <c r="AE6">
-        <v>0.1547647603609457</v>
+        <v>0.1820661488242576</v>
       </c>
       <c r="AF6">
-        <v>623.554764760361</v>
+        <v>602.8820661488243</v>
       </c>
       <c r="AG6">
-        <v>547.554764760361</v>
+        <v>523.5820661488243</v>
       </c>
       <c r="AH6">
-        <v>0.6385905289871694</v>
+        <v>0.6305096984061078</v>
       </c>
       <c r="AI6">
-        <v>0.30562593237399</v>
+        <v>0.3272829572730429</v>
       </c>
       <c r="AJ6">
-        <v>0.6080869202864203</v>
+        <v>0.5970951925705845</v>
       </c>
       <c r="AK6">
-        <v>0.2787595451383124</v>
+        <v>0.2970203045534163</v>
       </c>
       <c r="AL6">
-        <v>14.3</v>
+        <v>24.5</v>
       </c>
       <c r="AM6">
-        <v>14.3</v>
+        <v>24.5</v>
       </c>
       <c r="AN6">
-        <v>34.13085135505064</v>
+        <v>61.10716820440029</v>
       </c>
       <c r="AO6">
-        <v>1.111888111888112</v>
+        <v>0.3534693877551021</v>
       </c>
       <c r="AP6">
-        <v>29.97836105997049</v>
+        <v>53.0854776588081</v>
       </c>
       <c r="AQ6">
-        <v>1.111888111888112</v>
+        <v>0.3534693877551021</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.043215</v>
+        <v>-0.137</v>
       </c>
       <c r="E2">
-        <v>0.3975</v>
+        <v>-0.00207</v>
       </c>
       <c r="G2">
-        <v>0.06459671663097787</v>
+        <v>0.2289271422219399</v>
       </c>
       <c r="H2">
-        <v>0.06459671663097787</v>
+        <v>0.2289271422219399</v>
       </c>
       <c r="I2">
-        <v>0.1085798186891249</v>
+        <v>0.2305151495902941</v>
       </c>
       <c r="J2">
-        <v>0.1069814136978609</v>
+        <v>0.2269752977845463</v>
       </c>
       <c r="K2">
-        <v>-115.4</v>
+        <v>184.8</v>
       </c>
       <c r="L2">
-        <v>-0.04576096439051471</v>
+        <v>0.1173855046687417</v>
       </c>
       <c r="M2">
-        <v>28.074</v>
+        <v>89.7</v>
       </c>
       <c r="N2">
-        <v>0.008736268865722733</v>
+        <v>0.04709403055599307</v>
       </c>
       <c r="O2">
-        <v>-0.2432755632582323</v>
+        <v>0.4853896103896104</v>
       </c>
       <c r="P2">
-        <v>28.074</v>
+        <v>89.7</v>
       </c>
       <c r="Q2">
-        <v>0.008736268865722733</v>
+        <v>0.04709403055599307</v>
       </c>
       <c r="R2">
-        <v>-0.2432755632582323</v>
+        <v>0.4853896103896104</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>564.3</v>
+        <v>315.2</v>
       </c>
       <c r="V2">
-        <v>0.1756029251594834</v>
+        <v>0.1654853782747939</v>
       </c>
       <c r="W2">
-        <v>0.04928729238034837</v>
+        <v>0.08314212444324472</v>
       </c>
       <c r="X2">
-        <v>0.08017613765714045</v>
+        <v>0.0875652611939946</v>
       </c>
       <c r="Y2">
-        <v>-0.03088884527679207</v>
+        <v>-0.004423136750749887</v>
       </c>
       <c r="Z2">
-        <v>0.6491316742852689</v>
+        <v>0.6536704866301279</v>
       </c>
       <c r="AA2">
-        <v>0.1257511613995498</v>
+        <v>0.1483670533558426</v>
       </c>
       <c r="AB2">
-        <v>0.07626000355310386</v>
+        <v>0.07992222653886617</v>
       </c>
       <c r="AC2">
-        <v>0.04982686197366357</v>
+        <v>0.06844482681697646</v>
       </c>
       <c r="AD2">
-        <v>1216.13</v>
+        <v>565.3</v>
       </c>
       <c r="AE2">
-        <v>0.1820661488242576</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1216.312066148824</v>
+        <v>565.3</v>
       </c>
       <c r="AG2">
-        <v>652.0120661488243</v>
+        <v>250.1</v>
       </c>
       <c r="AH2">
-        <v>0.2745741914072345</v>
+        <v>0.2288663967611336</v>
       </c>
       <c r="AI2">
-        <v>0.2340676702820182</v>
+        <v>0.1834377129506441</v>
       </c>
       <c r="AJ2">
-        <v>0.1686741769243572</v>
+        <v>0.1160664562836458</v>
       </c>
       <c r="AK2">
-        <v>0.1407591303573345</v>
+        <v>0.0904030363274896</v>
       </c>
       <c r="AL2">
-        <v>63.802</v>
+        <v>37.3</v>
       </c>
       <c r="AM2">
-        <v>63.802</v>
+        <v>37.3</v>
       </c>
       <c r="AN2">
-        <v>4.201331430960089</v>
+        <v>1.504257583821181</v>
       </c>
       <c r="AO2">
-        <v>4.289207234882919</v>
+        <v>9.729222520107239</v>
       </c>
       <c r="AP2">
-        <v>2.252488456724432</v>
+        <v>0.6655135710484299</v>
       </c>
       <c r="AQ2">
-        <v>4.289207234882919</v>
+        <v>9.729222520107239</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Doha Insurance Group Q.P.S.C. (DSM:DOHI)</t>
+          <t>Qatar Insurance Company Q.S.P.C. (DSM:QATI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.167</v>
+        <v>-0.137</v>
       </c>
       <c r="E3">
-        <v>0.277</v>
+        <v>-0.00207</v>
       </c>
       <c r="G3">
-        <v>0.1758474576271186</v>
+        <v>0.2289271422219399</v>
       </c>
       <c r="H3">
-        <v>0.1758474576271186</v>
+        <v>0.2289271422219399</v>
       </c>
       <c r="I3">
-        <v>0.2208686440677966</v>
+        <v>0.2305151495902941</v>
       </c>
       <c r="J3">
-        <v>0.2208244703389831</v>
+        <v>0.2269752977845463</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>184.8</v>
       </c>
       <c r="L3">
-        <v>0.211864406779661</v>
+        <v>0.1173855046687417</v>
       </c>
       <c r="M3">
-        <v>20.6</v>
+        <v>89.7</v>
       </c>
       <c r="N3">
-        <v>0.06274748705452331</v>
+        <v>0.04709403055599307</v>
       </c>
       <c r="O3">
-        <v>0.515</v>
+        <v>0.4853896103896104</v>
       </c>
       <c r="P3">
-        <v>20.6</v>
+        <v>89.7</v>
       </c>
       <c r="Q3">
-        <v>0.06274748705452331</v>
+        <v>0.04709403055599307</v>
       </c>
       <c r="R3">
-        <v>0.515</v>
+        <v>0.4853896103896104</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,463 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>51.4</v>
+        <v>315.2</v>
       </c>
       <c r="V3">
-        <v>0.1565641181845873</v>
+        <v>0.1654853782747939</v>
       </c>
       <c r="W3">
-        <v>0.121765601217656</v>
+        <v>0.08314212444324472</v>
       </c>
       <c r="X3">
-        <v>0.07711541243361558</v>
+        <v>0.0875652611939946</v>
       </c>
       <c r="Y3">
-        <v>0.04465018878404042</v>
+        <v>-0.004423136750749887</v>
       </c>
       <c r="Z3">
-        <v>0.6018489002231432</v>
+        <v>0.6536704866301279</v>
       </c>
       <c r="AA3">
-        <v>0.1329029646158751</v>
+        <v>0.1483670533558426</v>
       </c>
       <c r="AB3">
-        <v>0.07568528559347776</v>
+        <v>0.07992222653886617</v>
       </c>
       <c r="AC3">
-        <v>0.0572176790223973</v>
+        <v>0.06844482681697646</v>
       </c>
       <c r="AD3">
-        <v>21.7</v>
+        <v>565.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.7</v>
+        <v>565.3</v>
       </c>
       <c r="AG3">
-        <v>-29.7</v>
+        <v>250.1</v>
       </c>
       <c r="AH3">
-        <v>0.062</v>
+        <v>0.2288663967611336</v>
       </c>
       <c r="AI3">
-        <v>0.06300813008130081</v>
+        <v>0.1834377129506441</v>
       </c>
       <c r="AJ3">
-        <v>-0.09946416610850635</v>
+        <v>0.1160664562836458</v>
       </c>
       <c r="AK3">
-        <v>-0.1013651877133106</v>
+        <v>0.0904030363274896</v>
       </c>
       <c r="AL3">
-        <v>0.302</v>
+        <v>37.3</v>
       </c>
       <c r="AM3">
-        <v>0.302</v>
+        <v>37.3</v>
       </c>
       <c r="AN3">
-        <v>0.4854586129753914</v>
+        <v>1.504257583821181</v>
       </c>
       <c r="AO3">
-        <v>138.0794701986755</v>
+        <v>9.729222520107239</v>
       </c>
       <c r="AP3">
-        <v>-0.6644295302013422</v>
+        <v>0.6655135710484299</v>
       </c>
       <c r="AQ3">
-        <v>138.0794701986755</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Qatar Insurance Company Q.S.P.C. (DSM:QATI)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.0757</v>
-      </c>
-      <c r="G4">
-        <v>0.04780326056921801</v>
-      </c>
-      <c r="H4">
-        <v>0.04780326056921801</v>
-      </c>
-      <c r="I4">
-        <v>0.09565257437597863</v>
-      </c>
-      <c r="J4">
-        <v>0.09003929348491646</v>
-      </c>
-      <c r="K4">
-        <v>-14.5</v>
-      </c>
-      <c r="L4">
-        <v>-0.00667771944367689</v>
-      </c>
-      <c r="M4">
-        <v>0.75</v>
-      </c>
-      <c r="N4">
-        <v>0.0003227750043036667</v>
-      </c>
-      <c r="O4">
-        <v>-0.05172413793103448</v>
-      </c>
-      <c r="P4">
-        <v>0.75</v>
-      </c>
-      <c r="Q4">
-        <v>0.0003227750043036667</v>
-      </c>
-      <c r="R4">
-        <v>-0.05172413793103448</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>404.9</v>
-      </c>
-      <c r="V4">
-        <v>0.1742554656567395</v>
-      </c>
-      <c r="W4">
-        <v>-0.00578472831724248</v>
-      </c>
-      <c r="X4">
-        <v>0.08323686288066531</v>
-      </c>
-      <c r="Y4">
-        <v>-0.0890215911979078</v>
-      </c>
-      <c r="Z4">
-        <v>1.468650659452148</v>
-      </c>
-      <c r="AA4">
-        <v>0.132236267753228</v>
-      </c>
-      <c r="AB4">
-        <v>0.07683472151272996</v>
-      </c>
-      <c r="AC4">
-        <v>0.05540154624049806</v>
-      </c>
-      <c r="AD4">
-        <v>590.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>590.6</v>
-      </c>
-      <c r="AG4">
-        <v>185.7</v>
-      </c>
-      <c r="AH4">
-        <v>0.202662823416375</v>
-      </c>
-      <c r="AI4">
-        <v>0.2072062589902817</v>
-      </c>
-      <c r="AJ4">
-        <v>0.07400470250667518</v>
-      </c>
-      <c r="AK4">
-        <v>0.0759384967694447</v>
-      </c>
-      <c r="AL4">
-        <v>39</v>
-      </c>
-      <c r="AM4">
-        <v>39</v>
-      </c>
-      <c r="AN4">
-        <v>2.711662075298439</v>
-      </c>
-      <c r="AO4">
-        <v>5.325641025641025</v>
-      </c>
-      <c r="AP4">
-        <v>0.8526170798898073</v>
-      </c>
-      <c r="AQ4">
-        <v>5.325641025641025</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Al Khaleej Takaful Insurance Company Q.P.S.C. (DSM:AKHI)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.07919999999999999</v>
-      </c>
-      <c r="E5">
-        <v>0.518</v>
-      </c>
-      <c r="G5">
-        <v>0.242566510172144</v>
-      </c>
-      <c r="H5">
-        <v>0.242566510172144</v>
-      </c>
-      <c r="I5">
-        <v>0.244131455399061</v>
-      </c>
-      <c r="J5">
-        <v>0.244131455399061</v>
-      </c>
-      <c r="K5">
-        <v>15.8</v>
-      </c>
-      <c r="L5">
-        <v>0.2472613458528952</v>
-      </c>
-      <c r="M5">
-        <v>6.57</v>
-      </c>
-      <c r="N5">
-        <v>0.03154104656745079</v>
-      </c>
-      <c r="O5">
-        <v>0.4158227848101266</v>
-      </c>
-      <c r="P5">
-        <v>6.57</v>
-      </c>
-      <c r="Q5">
-        <v>0.03154104656745079</v>
-      </c>
-      <c r="R5">
-        <v>0.4158227848101266</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>28.7</v>
-      </c>
-      <c r="V5">
-        <v>0.1377820451272203</v>
-      </c>
-      <c r="W5">
-        <v>0.1043593130779392</v>
-      </c>
-      <c r="X5">
-        <v>0.07514064091721216</v>
-      </c>
-      <c r="Y5">
-        <v>0.02921867216072707</v>
-      </c>
-      <c r="Z5">
-        <v>0.4885321100917432</v>
-      </c>
-      <c r="AA5">
-        <v>0.1192660550458716</v>
-      </c>
-      <c r="AB5">
-        <v>0.0750138773390425</v>
-      </c>
-      <c r="AC5">
-        <v>0.04425217770682907</v>
-      </c>
-      <c r="AD5">
-        <v>1.13</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1.13</v>
-      </c>
-      <c r="AG5">
-        <v>-27.57</v>
-      </c>
-      <c r="AH5">
-        <v>0.005395597574368523</v>
-      </c>
-      <c r="AI5">
-        <v>0.007078869886612792</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.1525479997786754</v>
-      </c>
-      <c r="AK5">
-        <v>-0.2105705338730619</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0.06608187134502923</v>
-      </c>
-      <c r="AP5">
-        <v>-1.612280701754386</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Qatar General Insurance &amp; Reinsurance Company Q.P.S.C. (DSM:QGRI)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.007229999999999999</v>
-      </c>
-      <c r="G6">
-        <v>0.1064483111566018</v>
-      </c>
-      <c r="H6">
-        <v>0.1064483111566018</v>
-      </c>
-      <c r="I6">
-        <v>0.09024142037088176</v>
-      </c>
-      <c r="J6">
-        <v>0.09024142037088176</v>
-      </c>
-      <c r="K6">
-        <v>-156.7</v>
-      </c>
-      <c r="L6">
-        <v>-1.60388945752303</v>
-      </c>
-      <c r="M6">
-        <v>0.154</v>
-      </c>
-      <c r="N6">
-        <v>0.0004358901783187093</v>
-      </c>
-      <c r="O6">
-        <v>-0.0009827696234843651</v>
-      </c>
-      <c r="P6">
-        <v>0.154</v>
-      </c>
-      <c r="Q6">
-        <v>0.0004358901783187093</v>
-      </c>
-      <c r="R6">
-        <v>-0.0009827696234843651</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>79.3</v>
-      </c>
-      <c r="V6">
-        <v>0.2244551372771016</v>
-      </c>
-      <c r="W6">
-        <v>-0.1107968606377713</v>
-      </c>
-      <c r="X6">
-        <v>0.1305044210073297</v>
-      </c>
-      <c r="Y6">
-        <v>-0.2413012816451011</v>
-      </c>
-      <c r="Z6">
-        <v>0.04979911977674844</v>
-      </c>
-      <c r="AA6">
-        <v>0.004493943301873447</v>
-      </c>
-      <c r="AB6">
-        <v>0.08229844230270678</v>
-      </c>
-      <c r="AC6">
-        <v>-0.07780449900083333</v>
-      </c>
-      <c r="AD6">
-        <v>602.7</v>
-      </c>
-      <c r="AE6">
-        <v>0.1820661488242576</v>
-      </c>
-      <c r="AF6">
-        <v>602.8820661488243</v>
-      </c>
-      <c r="AG6">
-        <v>523.5820661488243</v>
-      </c>
-      <c r="AH6">
-        <v>0.6305096984061078</v>
-      </c>
-      <c r="AI6">
-        <v>0.3272829572730429</v>
-      </c>
-      <c r="AJ6">
-        <v>0.5970951925705845</v>
-      </c>
-      <c r="AK6">
-        <v>0.2970203045534163</v>
-      </c>
-      <c r="AL6">
-        <v>24.5</v>
-      </c>
-      <c r="AM6">
-        <v>24.5</v>
-      </c>
-      <c r="AN6">
-        <v>61.10716820440029</v>
-      </c>
-      <c r="AO6">
-        <v>0.3534693877551021</v>
-      </c>
-      <c r="AP6">
-        <v>53.0854776588081</v>
-      </c>
-      <c r="AQ6">
-        <v>0.3534693877551021</v>
+        <v>9.729222520107239</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.137</v>
+        <v>0.11245</v>
       </c>
       <c r="E2">
-        <v>-0.00207</v>
+        <v>0.125</v>
       </c>
       <c r="G2">
-        <v>0.2289271422219399</v>
+        <v>0.1475733263185584</v>
       </c>
       <c r="H2">
-        <v>0.2289271422219399</v>
+        <v>0.1475733263185584</v>
       </c>
       <c r="I2">
-        <v>0.2305151495902941</v>
+        <v>0.1551142093033452</v>
       </c>
       <c r="J2">
-        <v>0.2269752977845463</v>
+        <v>0.1545083052140801</v>
       </c>
       <c r="K2">
-        <v>184.8</v>
+        <v>-144.6</v>
       </c>
       <c r="L2">
-        <v>0.1173855046687417</v>
+        <v>-0.06339602788373008</v>
       </c>
       <c r="M2">
-        <v>89.7</v>
+        <v>122.41</v>
       </c>
       <c r="N2">
-        <v>0.04709403055599307</v>
+        <v>0.04545994726482713</v>
       </c>
       <c r="O2">
-        <v>0.4853896103896104</v>
+        <v>-0.846542185338866</v>
       </c>
       <c r="P2">
-        <v>89.7</v>
+        <v>122.41</v>
       </c>
       <c r="Q2">
-        <v>0.04709403055599307</v>
+        <v>0.04545994726482713</v>
       </c>
       <c r="R2">
-        <v>0.4853896103896104</v>
+        <v>-0.846542185338866</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>315.2</v>
+        <v>477.8</v>
       </c>
       <c r="V2">
-        <v>0.1654853782747939</v>
+        <v>0.1774427154900286</v>
       </c>
       <c r="W2">
-        <v>0.08314212444324472</v>
+        <v>0.1024543429787202</v>
       </c>
       <c r="X2">
-        <v>0.0875652611939946</v>
+        <v>0.08367134870248624</v>
       </c>
       <c r="Y2">
-        <v>-0.004423136750749887</v>
+        <v>0.01878299427623391</v>
       </c>
       <c r="Z2">
-        <v>0.6536704866301279</v>
+        <v>0.4967408797991172</v>
       </c>
       <c r="AA2">
-        <v>0.1483670533558426</v>
+        <v>0.1514665282584239</v>
       </c>
       <c r="AB2">
-        <v>0.07992222653886617</v>
+        <v>0.07945116370757183</v>
       </c>
       <c r="AC2">
-        <v>0.06844482681697646</v>
+        <v>0.07201536455085203</v>
       </c>
       <c r="AD2">
-        <v>565.3</v>
+        <v>874.2099999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>565.3</v>
+        <v>874.2099999999999</v>
       </c>
       <c r="AG2">
-        <v>250.1</v>
+        <v>396.4099999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2288663967611336</v>
+        <v>0.2450888864591481</v>
       </c>
       <c r="AI2">
-        <v>0.1834377129506441</v>
+        <v>0.1800523550504499</v>
       </c>
       <c r="AJ2">
-        <v>0.1160664562836458</v>
+        <v>0.1283249868084982</v>
       </c>
       <c r="AK2">
-        <v>0.0904030363274896</v>
+        <v>0.09055604670234903</v>
       </c>
       <c r="AL2">
-        <v>37.3</v>
+        <v>59.422</v>
       </c>
       <c r="AM2">
-        <v>37.3</v>
+        <v>59.422</v>
       </c>
       <c r="AN2">
-        <v>1.504257583821181</v>
+        <v>2.361453268503511</v>
       </c>
       <c r="AO2">
-        <v>9.729222520107239</v>
+        <v>5.95402376224294</v>
       </c>
       <c r="AP2">
-        <v>0.6655135710484299</v>
+        <v>1.070799567801188</v>
       </c>
       <c r="AQ2">
-        <v>9.729222520107239</v>
+        <v>5.95402376224294</v>
       </c>
     </row>
     <row r="3">
@@ -713,130 +713,520 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Al Khaleej Takaful Insurance Company Q.P.S.C. (DSM:AKHI)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0629</v>
+      </c>
+      <c r="E3">
+        <v>0.125</v>
+      </c>
+      <c r="G3">
+        <v>0.2590604026845638</v>
+      </c>
+      <c r="H3">
+        <v>0.2590604026845638</v>
+      </c>
+      <c r="I3">
+        <v>0.2751677852348993</v>
+      </c>
+      <c r="J3">
+        <v>0.2751677852348993</v>
+      </c>
+      <c r="K3">
+        <v>19.3</v>
+      </c>
+      <c r="L3">
+        <v>0.2590604026845638</v>
+      </c>
+      <c r="M3">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.052</v>
+      </c>
+      <c r="O3">
+        <v>0.4512953367875648</v>
+      </c>
+      <c r="P3">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="Q3">
+        <v>0.052</v>
+      </c>
+      <c r="R3">
+        <v>0.4512953367875648</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>33.2</v>
+      </c>
+      <c r="V3">
+        <v>0.1982089552238806</v>
+      </c>
+      <c r="W3">
+        <v>0.1217665615141956</v>
+      </c>
+      <c r="X3">
+        <v>0.07894116878026036</v>
+      </c>
+      <c r="Y3">
+        <v>0.04282539273393522</v>
+      </c>
+      <c r="Z3">
+        <v>0.5690063392652562</v>
+      </c>
+      <c r="AA3">
+        <v>0.1565722141602383</v>
+      </c>
+      <c r="AB3">
+        <v>0.07877809477577338</v>
+      </c>
+      <c r="AC3">
+        <v>0.0777941193844649</v>
+      </c>
+      <c r="AD3">
+        <v>1.11</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.11</v>
+      </c>
+      <c r="AG3">
+        <v>-32.09</v>
+      </c>
+      <c r="AH3">
+        <v>0.006583239428266414</v>
+      </c>
+      <c r="AI3">
+        <v>0.006517526862779638</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.2369839745956724</v>
+      </c>
+      <c r="AK3">
+        <v>-0.234045656771935</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0.05362318840579711</v>
+      </c>
+      <c r="AP3">
+        <v>-1.55024154589372</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Doha Insurance Group Q.P.S.C. (DSM:DOHI)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.384</v>
+      </c>
+      <c r="E4">
+        <v>0.202</v>
+      </c>
+      <c r="G4">
+        <v>0.1021062271062271</v>
+      </c>
+      <c r="H4">
+        <v>0.1021062271062271</v>
+      </c>
+      <c r="I4">
+        <v>0.1037087912087912</v>
+      </c>
+      <c r="J4">
+        <v>0.1036809499225606</v>
+      </c>
+      <c r="K4">
+        <v>44.7</v>
+      </c>
+      <c r="L4">
+        <v>0.1023351648351648</v>
+      </c>
+      <c r="M4">
+        <v>24</v>
+      </c>
+      <c r="N4">
+        <v>0.06988934187536401</v>
+      </c>
+      <c r="O4">
+        <v>0.5369127516778524</v>
+      </c>
+      <c r="P4">
+        <v>24</v>
+      </c>
+      <c r="Q4">
+        <v>0.06988934187536401</v>
+      </c>
+      <c r="R4">
+        <v>0.5369127516778524</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>52.5</v>
+      </c>
+      <c r="V4">
+        <v>0.1528829353523588</v>
+      </c>
+      <c r="W4">
+        <v>0.1385187480632166</v>
+      </c>
+      <c r="X4">
+        <v>0.07979806634569621</v>
+      </c>
+      <c r="Y4">
+        <v>0.05872068171752041</v>
+      </c>
+      <c r="Z4">
+        <v>1.490784982935154</v>
+      </c>
+      <c r="AA4">
+        <v>0.1545660031610051</v>
+      </c>
+      <c r="AB4">
+        <v>0.07899600946639815</v>
+      </c>
+      <c r="AC4">
+        <v>0.07556999369460696</v>
+      </c>
+      <c r="AD4">
+        <v>12.2</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>12.2</v>
+      </c>
+      <c r="AG4">
+        <v>-40.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.0343082114735658</v>
+      </c>
+      <c r="AI4">
+        <v>0.03373893805309735</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.1329594193335533</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1303785182788741</v>
+      </c>
+      <c r="AL4">
+        <v>0.722</v>
+      </c>
+      <c r="AM4">
+        <v>0.722</v>
+      </c>
+      <c r="AN4">
+        <v>0.2525879917184265</v>
+      </c>
+      <c r="AO4">
+        <v>62.74238227146814</v>
+      </c>
+      <c r="AP4">
+        <v>-0.8343685300207039</v>
+      </c>
+      <c r="AQ4">
+        <v>62.74238227146814</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Qatar Insurance Company Q.S.P.C. (DSM:QATI)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>-0.137</v>
       </c>
-      <c r="E3">
+      <c r="E5">
         <v>-0.00207</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>0.2289271422219399</v>
       </c>
-      <c r="H3">
+      <c r="H5">
         <v>0.2289271422219399</v>
       </c>
-      <c r="I3">
+      <c r="I5">
         <v>0.2305151495902941</v>
       </c>
-      <c r="J3">
+      <c r="J5">
         <v>0.2269752977845463</v>
       </c>
-      <c r="K3">
+      <c r="K5">
         <v>184.8</v>
       </c>
-      <c r="L3">
+      <c r="L5">
         <v>0.1173855046687417</v>
       </c>
-      <c r="M3">
+      <c r="M5">
         <v>89.7</v>
       </c>
-      <c r="N3">
+      <c r="N5">
         <v>0.04709403055599307</v>
       </c>
-      <c r="O3">
+      <c r="O5">
         <v>0.4853896103896104</v>
       </c>
-      <c r="P3">
+      <c r="P5">
         <v>89.7</v>
       </c>
-      <c r="Q3">
+      <c r="Q5">
         <v>0.04709403055599307</v>
       </c>
-      <c r="R3">
+      <c r="R5">
         <v>0.4853896103896104</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>315.2</v>
       </c>
-      <c r="V3">
+      <c r="V5">
         <v>0.1654853782747939</v>
       </c>
-      <c r="W3">
+      <c r="W5">
         <v>0.08314212444324472</v>
       </c>
-      <c r="X3">
-        <v>0.0875652611939946</v>
-      </c>
-      <c r="Y3">
-        <v>-0.004423136750749887</v>
-      </c>
-      <c r="Z3">
+      <c r="X5">
+        <v>0.08754463105927626</v>
+      </c>
+      <c r="Y5">
+        <v>-0.004402506616031546</v>
+      </c>
+      <c r="Z5">
         <v>0.6536704866301279</v>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <v>0.1483670533558426</v>
       </c>
-      <c r="AB3">
-        <v>0.07992222653886617</v>
-      </c>
-      <c r="AC3">
-        <v>0.06844482681697646</v>
-      </c>
-      <c r="AD3">
+      <c r="AB5">
+        <v>0.07990631794874552</v>
+      </c>
+      <c r="AC5">
+        <v>0.06846073540709711</v>
+      </c>
+      <c r="AD5">
         <v>565.3</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>565.3</v>
       </c>
-      <c r="AG3">
+      <c r="AG5">
         <v>250.1</v>
       </c>
-      <c r="AH3">
+      <c r="AH5">
         <v>0.2288663967611336</v>
       </c>
-      <c r="AI3">
+      <c r="AI5">
         <v>0.1834377129506441</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ5">
         <v>0.1160664562836458</v>
       </c>
-      <c r="AK3">
+      <c r="AK5">
         <v>0.0904030363274896</v>
       </c>
-      <c r="AL3">
+      <c r="AL5">
         <v>37.3</v>
       </c>
-      <c r="AM3">
+      <c r="AM5">
         <v>37.3</v>
       </c>
-      <c r="AN3">
+      <c r="AN5">
         <v>1.504257583821181</v>
       </c>
-      <c r="AO3">
+      <c r="AO5">
         <v>9.729222520107239</v>
       </c>
-      <c r="AP3">
+      <c r="AP5">
         <v>0.6655135710484299</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ5">
         <v>9.729222520107239</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Qatar General Insurance &amp; Reinsurance Company Q.P.S.C. (DSM:QGRI)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.162</v>
+      </c>
+      <c r="G6">
+        <v>-0.44905273937532</v>
+      </c>
+      <c r="H6">
+        <v>-0.44905273937532</v>
+      </c>
+      <c r="I6">
+        <v>-0.3835125448028674</v>
+      </c>
+      <c r="J6">
+        <v>-0.3835125448028674</v>
+      </c>
+      <c r="K6">
+        <v>-393.4</v>
+      </c>
+      <c r="L6">
+        <v>-2.014336917562724</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="V6">
+        <v>0.2775171418260556</v>
+      </c>
+      <c r="W6">
+        <v>-0.3182847896440129</v>
+      </c>
+      <c r="X6">
+        <v>0.1103744277573568</v>
+      </c>
+      <c r="Y6">
+        <v>-0.4286592174013697</v>
+      </c>
+      <c r="Z6">
+        <v>0.1110037512788451</v>
+      </c>
+      <c r="AA6">
+        <v>-0.04257133113561441</v>
+      </c>
+      <c r="AB6">
+        <v>0.08252580714604593</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1250971382816604</v>
+      </c>
+      <c r="AD6">
+        <v>295.6</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>295.6</v>
+      </c>
+      <c r="AG6">
+        <v>218.7</v>
+      </c>
+      <c r="AH6">
+        <v>0.5161515627728305</v>
+      </c>
+      <c r="AI6">
+        <v>0.2380607232020617</v>
+      </c>
+      <c r="AJ6">
+        <v>0.4411052843888664</v>
+      </c>
+      <c r="AK6">
+        <v>0.187757554945055</v>
+      </c>
+      <c r="AL6">
+        <v>21.4</v>
+      </c>
+      <c r="AM6">
+        <v>21.4</v>
+      </c>
+      <c r="AN6">
+        <v>-3.962466487935657</v>
+      </c>
+      <c r="AO6">
+        <v>-3.5</v>
+      </c>
+      <c r="AP6">
+        <v>-2.931635388739947</v>
+      </c>
+      <c r="AQ6">
+        <v>-3.5</v>
       </c>
     </row>
   </sheetData>
